--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1922" uniqueCount="891">
   <si>
     <t>EA</t>
   </si>
@@ -5362,6 +5362,20 @@
       <t xml:space="preserve">
 </t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>i-mob7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>. GPS 기반 위치 추적 단말기
+. 관리자가 설정한 범위 안에서만 추적 가능
+. GPS 데이터 수집 및 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPS 단말기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13236,7 +13250,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.875" style="58" customWidth="1"/>
@@ -13941,22 +13955,22 @@
     </row>
     <row r="34" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="55" t="s">
-        <v>677</v>
+        <v>66</v>
       </c>
       <c r="B34" s="55" t="s">
-        <v>16</v>
+        <v>888</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>820</v>
+        <v>890</v>
       </c>
       <c r="D34" s="56" t="s">
-        <v>821</v>
+        <v>889</v>
       </c>
       <c r="E34" s="55">
         <v>1</v>
       </c>
       <c r="F34" s="57">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="G34" s="55"/>
     </row>
@@ -13965,19 +13979,19 @@
         <v>677</v>
       </c>
       <c r="B35" s="55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" s="55" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D35" s="56" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E35" s="55">
         <v>1</v>
       </c>
       <c r="F35" s="57">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="G35" s="55"/>
     </row>
@@ -13986,19 +14000,19 @@
         <v>677</v>
       </c>
       <c r="B36" s="55" t="s">
-        <v>717</v>
+        <v>17</v>
       </c>
       <c r="C36" s="55" t="s">
-        <v>775</v>
+        <v>822</v>
       </c>
       <c r="D36" s="56" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E36" s="55">
         <v>1</v>
       </c>
       <c r="F36" s="57">
-        <v>1200000</v>
+        <v>800000</v>
       </c>
       <c r="G36" s="55"/>
     </row>
@@ -14007,19 +14021,19 @@
         <v>677</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C37" s="55" t="s">
-        <v>825</v>
+        <v>775</v>
       </c>
       <c r="D37" s="56" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="E37" s="55">
         <v>1</v>
       </c>
       <c r="F37" s="57">
-        <v>1400000</v>
+        <v>1200000</v>
       </c>
       <c r="G37" s="55"/>
     </row>
@@ -14028,19 +14042,19 @@
         <v>677</v>
       </c>
       <c r="B38" s="55" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C38" s="55" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E38" s="55">
         <v>1</v>
       </c>
       <c r="F38" s="57">
-        <v>1600000</v>
+        <v>1400000</v>
       </c>
       <c r="G38" s="55"/>
     </row>
@@ -14049,19 +14063,19 @@
         <v>677</v>
       </c>
       <c r="B39" s="55" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C39" s="55" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D39" s="56" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="E39" s="55">
         <v>1</v>
       </c>
       <c r="F39" s="57">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="G39" s="55"/>
     </row>
@@ -14070,19 +14084,19 @@
         <v>677</v>
       </c>
       <c r="B40" s="55" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C40" s="55" t="s">
-        <v>766</v>
+        <v>829</v>
       </c>
       <c r="D40" s="56" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E40" s="55">
         <v>1</v>
       </c>
       <c r="F40" s="57">
-        <v>300000</v>
+        <v>250000</v>
       </c>
       <c r="G40" s="55"/>
     </row>
@@ -14091,19 +14105,19 @@
         <v>677</v>
       </c>
       <c r="B41" s="55" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C41" s="55" t="s">
-        <v>23</v>
+        <v>766</v>
       </c>
       <c r="D41" s="56" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E41" s="55">
         <v>1</v>
       </c>
       <c r="F41" s="57">
-        <v>450000</v>
+        <v>300000</v>
       </c>
       <c r="G41" s="55"/>
     </row>
@@ -14112,19 +14126,19 @@
         <v>677</v>
       </c>
       <c r="B42" s="55" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C42" s="55" t="s">
-        <v>833</v>
+        <v>23</v>
       </c>
       <c r="D42" s="56" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="E42" s="55">
         <v>1</v>
       </c>
       <c r="F42" s="57">
-        <v>500000</v>
+        <v>450000</v>
       </c>
       <c r="G42" s="55"/>
     </row>
@@ -14133,40 +14147,40 @@
         <v>677</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C43" s="55" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D43" s="56" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E43" s="55">
         <v>1</v>
       </c>
       <c r="F43" s="57">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="G43" s="55"/>
     </row>
-    <row r="44" spans="1:7" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="55" t="s">
         <v>677</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C44" s="55" t="s">
-        <v>39</v>
+        <v>835</v>
       </c>
       <c r="D44" s="56" t="s">
-        <v>42</v>
+        <v>836</v>
       </c>
       <c r="E44" s="55">
         <v>1</v>
       </c>
       <c r="F44" s="57">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="G44" s="55"/>
     </row>
@@ -14175,19 +14189,19 @@
         <v>677</v>
       </c>
       <c r="B45" s="55" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C45" s="55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D45" s="56" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E45" s="55">
         <v>1</v>
       </c>
       <c r="F45" s="57">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="G45" s="55"/>
     </row>
@@ -14196,13 +14210,13 @@
         <v>677</v>
       </c>
       <c r="B46" s="55" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C46" s="55" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D46" s="56" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E46" s="55">
         <v>1</v>
@@ -14212,18 +14226,18 @@
       </c>
       <c r="G46" s="55"/>
     </row>
-    <row r="47" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="55" t="s">
         <v>677</v>
       </c>
       <c r="B47" s="55" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C47" s="55" t="s">
-        <v>772</v>
+        <v>41</v>
       </c>
       <c r="D47" s="56" t="s">
-        <v>837</v>
+        <v>44</v>
       </c>
       <c r="E47" s="55">
         <v>1</v>
@@ -14238,19 +14252,19 @@
         <v>677</v>
       </c>
       <c r="B48" s="55" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C48" s="55" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="D48" s="56" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E48" s="55">
         <v>1</v>
       </c>
       <c r="F48" s="57">
-        <v>500000</v>
+        <v>100000</v>
       </c>
       <c r="G48" s="55"/>
     </row>
@@ -14259,40 +14273,40 @@
         <v>677</v>
       </c>
       <c r="B49" s="55" t="s">
-        <v>629</v>
+        <v>729</v>
       </c>
       <c r="C49" s="55" t="s">
-        <v>773</v>
+        <v>778</v>
       </c>
       <c r="D49" s="56" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E49" s="55">
         <v>1</v>
       </c>
       <c r="F49" s="57">
-        <v>100000</v>
+        <v>500000</v>
       </c>
       <c r="G49" s="55"/>
     </row>
     <row r="50" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="55" t="s">
-        <v>840</v>
+        <v>677</v>
       </c>
       <c r="B50" s="55" t="s">
-        <v>730</v>
+        <v>629</v>
       </c>
       <c r="C50" s="55" t="s">
-        <v>841</v>
+        <v>773</v>
       </c>
       <c r="D50" s="56" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="E50" s="55">
         <v>1</v>
       </c>
       <c r="F50" s="57">
-        <v>6000000</v>
+        <v>100000</v>
       </c>
       <c r="G50" s="55"/>
     </row>
@@ -14301,19 +14315,19 @@
         <v>840</v>
       </c>
       <c r="B51" s="55" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C51" s="55" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D51" s="56" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="E51" s="55">
         <v>1</v>
       </c>
       <c r="F51" s="57">
-        <v>8000000</v>
+        <v>6000000</v>
       </c>
       <c r="G51" s="55"/>
     </row>
@@ -14322,19 +14336,19 @@
         <v>840</v>
       </c>
       <c r="B52" s="55" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C52" s="55" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D52" s="56" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E52" s="55">
         <v>1</v>
       </c>
       <c r="F52" s="57">
-        <v>1500000</v>
+        <v>8000000</v>
       </c>
       <c r="G52" s="55"/>
     </row>
@@ -14343,40 +14357,40 @@
         <v>840</v>
       </c>
       <c r="B53" s="55" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C53" s="55" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D53" s="56" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="E53" s="55">
         <v>1</v>
       </c>
       <c r="F53" s="57">
-        <v>100000</v>
+        <v>1500000</v>
       </c>
       <c r="G53" s="55"/>
     </row>
     <row r="54" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="55" t="s">
-        <v>67</v>
+        <v>840</v>
       </c>
       <c r="B54" s="55" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C54" s="55" t="s">
-        <v>776</v>
+        <v>847</v>
       </c>
       <c r="D54" s="56" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E54" s="55">
         <v>1</v>
       </c>
       <c r="F54" s="57">
-        <v>2000000</v>
+        <v>100000</v>
       </c>
       <c r="G54" s="55"/>
     </row>
@@ -14385,19 +14399,19 @@
         <v>67</v>
       </c>
       <c r="B55" s="55" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C55" s="55" t="s">
-        <v>850</v>
+        <v>776</v>
       </c>
       <c r="D55" s="56" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E55" s="55">
         <v>1</v>
       </c>
       <c r="F55" s="57">
-        <v>2700000</v>
+        <v>2000000</v>
       </c>
       <c r="G55" s="55"/>
     </row>
@@ -14406,19 +14420,19 @@
         <v>67</v>
       </c>
       <c r="B56" s="55" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C56" s="55" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D56" s="56" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E56" s="55">
         <v>1</v>
       </c>
       <c r="F56" s="57">
-        <v>4000000</v>
+        <v>2700000</v>
       </c>
       <c r="G56" s="55"/>
     </row>
@@ -14427,19 +14441,19 @@
         <v>67</v>
       </c>
       <c r="B57" s="55" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C57" s="55" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D57" s="56" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E57" s="55">
         <v>1</v>
       </c>
       <c r="F57" s="57">
-        <v>1100000</v>
+        <v>4000000</v>
       </c>
       <c r="G57" s="55"/>
     </row>
@@ -14448,19 +14462,19 @@
         <v>67</v>
       </c>
       <c r="B58" s="55" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C58" s="55" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D58" s="56" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E58" s="55">
         <v>1</v>
       </c>
       <c r="F58" s="57">
-        <v>1300000</v>
+        <v>1100000</v>
       </c>
       <c r="G58" s="55"/>
     </row>
@@ -14469,19 +14483,19 @@
         <v>67</v>
       </c>
       <c r="B59" s="55" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C59" s="55" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D59" s="56" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E59" s="55">
         <v>1</v>
       </c>
       <c r="F59" s="57">
-        <v>1600000</v>
+        <v>1300000</v>
       </c>
       <c r="G59" s="55"/>
     </row>
@@ -14490,19 +14504,19 @@
         <v>67</v>
       </c>
       <c r="B60" s="55" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C60" s="55" t="s">
-        <v>741</v>
+        <v>858</v>
       </c>
       <c r="D60" s="56" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E60" s="55">
         <v>1</v>
       </c>
       <c r="F60" s="57">
-        <v>450000</v>
+        <v>1600000</v>
       </c>
       <c r="G60" s="55"/>
     </row>
@@ -14511,40 +14525,40 @@
         <v>67</v>
       </c>
       <c r="B61" s="55" t="s">
-        <v>68</v>
+        <v>740</v>
       </c>
       <c r="C61" s="55" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D61" s="56" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E61" s="55">
         <v>1</v>
       </c>
       <c r="F61" s="57">
-        <v>700000</v>
+        <v>450000</v>
       </c>
       <c r="G61" s="55"/>
     </row>
     <row r="62" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="55" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B62" s="55" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="C62" s="55" t="s">
-        <v>29</v>
+        <v>742</v>
       </c>
       <c r="D62" s="56" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E62" s="55">
         <v>1</v>
       </c>
       <c r="F62" s="57">
-        <v>1100000</v>
+        <v>700000</v>
       </c>
       <c r="G62" s="55"/>
     </row>
@@ -14553,7 +14567,7 @@
         <v>69</v>
       </c>
       <c r="B63" s="55" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C63" s="55" t="s">
         <v>29</v>
@@ -14565,45 +14579,45 @@
         <v>1</v>
       </c>
       <c r="F63" s="57">
-        <v>500000</v>
-      </c>
-      <c r="G63" s="55" t="s">
-        <v>885</v>
-      </c>
+        <v>1100000</v>
+      </c>
+      <c r="G63" s="55"/>
     </row>
     <row r="64" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="55" t="s">
         <v>69</v>
       </c>
       <c r="B64" s="55" t="s">
-        <v>743</v>
+        <v>24</v>
       </c>
       <c r="C64" s="55" t="s">
-        <v>863</v>
+        <v>29</v>
       </c>
       <c r="D64" s="56" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E64" s="55">
         <v>1</v>
       </c>
       <c r="F64" s="57">
-        <v>200000</v>
-      </c>
-      <c r="G64" s="55"/>
+        <v>500000</v>
+      </c>
+      <c r="G64" s="55" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="65" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="55" t="s">
         <v>69</v>
       </c>
       <c r="B65" s="55" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C65" s="55" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D65" s="56" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E65" s="55">
         <v>1</v>
@@ -14618,40 +14632,40 @@
         <v>69</v>
       </c>
       <c r="B66" s="55" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C66" s="55" t="s">
-        <v>772</v>
+        <v>865</v>
       </c>
       <c r="D66" s="56" t="s">
-        <v>837</v>
+        <v>866</v>
       </c>
       <c r="E66" s="55">
         <v>1</v>
       </c>
       <c r="F66" s="57">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="G66" s="55"/>
     </row>
     <row r="67" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="55" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="B67" s="55" t="s">
-        <v>54</v>
+        <v>745</v>
       </c>
       <c r="C67" s="55" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="D67" s="56" t="s">
-        <v>867</v>
+        <v>837</v>
       </c>
       <c r="E67" s="55">
         <v>1</v>
       </c>
       <c r="F67" s="57">
-        <v>600000</v>
+        <v>150000</v>
       </c>
       <c r="G67" s="55"/>
     </row>
@@ -14660,19 +14674,19 @@
         <v>21</v>
       </c>
       <c r="B68" s="55" t="s">
-        <v>746</v>
+        <v>54</v>
       </c>
       <c r="C68" s="55" t="s">
-        <v>868</v>
+        <v>781</v>
       </c>
       <c r="D68" s="56" t="s">
-        <v>747</v>
+        <v>867</v>
       </c>
       <c r="E68" s="55">
         <v>1</v>
       </c>
       <c r="F68" s="57">
-        <v>800000</v>
+        <v>600000</v>
       </c>
       <c r="G68" s="55"/>
     </row>
@@ -14681,19 +14695,19 @@
         <v>21</v>
       </c>
       <c r="B69" s="55" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C69" s="55" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="D69" s="56" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E69" s="55">
         <v>1</v>
       </c>
       <c r="F69" s="57">
-        <v>1300000</v>
+        <v>800000</v>
       </c>
       <c r="G69" s="55"/>
     </row>
@@ -14702,19 +14716,19 @@
         <v>21</v>
       </c>
       <c r="B70" s="55" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C70" s="55" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="D70" s="56" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E70" s="55">
         <v>1</v>
       </c>
       <c r="F70" s="57">
-        <v>2000000</v>
+        <v>1300000</v>
       </c>
       <c r="G70" s="55"/>
     </row>
@@ -14723,19 +14737,19 @@
         <v>21</v>
       </c>
       <c r="B71" s="55" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C71" s="55" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D71" s="56" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E71" s="55">
         <v>1</v>
       </c>
       <c r="F71" s="57">
-        <v>3500000</v>
+        <v>2000000</v>
       </c>
       <c r="G71" s="55"/>
     </row>
@@ -14744,10 +14758,10 @@
         <v>21</v>
       </c>
       <c r="B72" s="55" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C72" s="55" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="D72" s="56" t="s">
         <v>753</v>
@@ -14756,7 +14770,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="57">
-        <v>2000000</v>
+        <v>3500000</v>
       </c>
       <c r="G72" s="55"/>
     </row>
@@ -14765,19 +14779,19 @@
         <v>21</v>
       </c>
       <c r="B73" s="55" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C73" s="55" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="D73" s="56" t="s">
-        <v>874</v>
+        <v>753</v>
       </c>
       <c r="E73" s="55">
         <v>1</v>
       </c>
       <c r="F73" s="57">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="G73" s="55"/>
     </row>
@@ -14786,19 +14800,19 @@
         <v>21</v>
       </c>
       <c r="B74" s="55" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C74" s="55" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D74" s="56" t="s">
-        <v>757</v>
+        <v>874</v>
       </c>
       <c r="E74" s="55">
         <v>1</v>
       </c>
       <c r="F74" s="57">
-        <v>250000</v>
+        <v>3000000</v>
       </c>
       <c r="G74" s="55"/>
     </row>
@@ -14807,19 +14821,19 @@
         <v>21</v>
       </c>
       <c r="B75" s="55" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C75" s="55" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="D75" s="56" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E75" s="55">
         <v>1</v>
       </c>
       <c r="F75" s="57">
-        <v>700000</v>
+        <v>250000</v>
       </c>
       <c r="G75" s="55"/>
     </row>
@@ -14828,19 +14842,19 @@
         <v>21</v>
       </c>
       <c r="B76" s="55" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C76" s="55" t="s">
-        <v>34</v>
+        <v>876</v>
       </c>
       <c r="D76" s="56" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E76" s="55">
         <v>1</v>
       </c>
       <c r="F76" s="57">
-        <v>300000</v>
+        <v>700000</v>
       </c>
       <c r="G76" s="55"/>
     </row>
@@ -14849,13 +14863,13 @@
         <v>21</v>
       </c>
       <c r="B77" s="55" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C77" s="55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D77" s="56" t="s">
-        <v>877</v>
+        <v>761</v>
       </c>
       <c r="E77" s="55">
         <v>1</v>
@@ -14867,66 +14881,66 @@
     </row>
     <row r="78" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="55" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B78" s="55" t="s">
-        <v>51</v>
+        <v>762</v>
       </c>
       <c r="C78" s="55" t="s">
-        <v>878</v>
+        <v>35</v>
       </c>
       <c r="D78" s="56" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="E78" s="55">
         <v>1</v>
       </c>
       <c r="F78" s="57">
-        <v>2000000</v>
-      </c>
-      <c r="G78" s="55" t="s">
-        <v>887</v>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="G78" s="55"/>
     </row>
     <row r="79" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="55" t="s">
         <v>49</v>
       </c>
       <c r="B79" s="55" t="s">
-        <v>763</v>
+        <v>51</v>
       </c>
       <c r="C79" s="55" t="s">
-        <v>50</v>
+        <v>878</v>
       </c>
       <c r="D79" s="56" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="E79" s="55">
         <v>1</v>
       </c>
       <c r="F79" s="57">
-        <v>10000</v>
-      </c>
-      <c r="G79" s="55"/>
+        <v>2000000</v>
+      </c>
+      <c r="G79" s="55" t="s">
+        <v>887</v>
+      </c>
     </row>
     <row r="80" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="55" t="s">
         <v>49</v>
       </c>
       <c r="B80" s="55" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C80" s="55" t="s">
-        <v>880</v>
+        <v>50</v>
       </c>
       <c r="D80" s="56" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="E80" s="55">
         <v>1</v>
       </c>
       <c r="F80" s="57">
-        <v>70000</v>
+        <v>10000</v>
       </c>
       <c r="G80" s="55"/>
     </row>
@@ -14935,21 +14949,42 @@
         <v>49</v>
       </c>
       <c r="B81" s="55" t="s">
+        <v>764</v>
+      </c>
+      <c r="C81" s="55" t="s">
+        <v>880</v>
+      </c>
+      <c r="D81" s="56" t="s">
+        <v>881</v>
+      </c>
+      <c r="E81" s="55">
+        <v>1</v>
+      </c>
+      <c r="F81" s="57">
+        <v>70000</v>
+      </c>
+      <c r="G81" s="55"/>
+    </row>
+    <row r="82" spans="1:7" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="B82" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="C81" s="55" t="s">
+      <c r="C82" s="55" t="s">
         <v>882</v>
       </c>
-      <c r="D81" s="56" t="s">
+      <c r="D82" s="56" t="s">
         <v>883</v>
       </c>
-      <c r="E81" s="55">
-        <v>1</v>
-      </c>
-      <c r="F81" s="57">
+      <c r="E82" s="55">
+        <v>1</v>
+      </c>
+      <c r="F82" s="57">
         <v>40000</v>
       </c>
-      <c r="G81" s="55"/>
+      <c r="G82" s="55"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/catalog.xlsx
+++ b/data/catalog.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20280" windowHeight="10470" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20280" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="단품목록" sheetId="3" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2159" uniqueCount="998">
   <si>
     <t>EA</t>
   </si>
@@ -3218,10 +3218,6 @@
 - NVR/DVR 재등록, 영상 출력 및 녹화 상태 확인
 . 자재 및 마감 비용
 - 브라켓, 앙카, 피스 등 설치 자재 및 배선 마감 처리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>태양발전시스템(24시간 기준)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -4475,6 +4471,14 @@
   </si>
   <si>
     <t>오거 크레인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태양발전시스템(12시간 기준)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>태양발전시스템(12시간 기준)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5237,7 +5241,7 @@
     <col min="1" max="1" width="16.875" style="23" customWidth="1"/>
     <col min="2" max="2" width="14.75" style="23" customWidth="1"/>
     <col min="3" max="3" width="25" style="23" customWidth="1"/>
-    <col min="4" max="4" width="55.625" style="24" customWidth="1"/>
+    <col min="4" max="4" width="57.375" style="24" customWidth="1"/>
     <col min="5" max="5" width="9.375" style="25" customWidth="1"/>
     <col min="6" max="6" width="16.625" style="25" customWidth="1"/>
     <col min="7" max="7" width="30.625" style="25" customWidth="1"/>
@@ -5245,28 +5249,28 @@
   <sheetData>
     <row r="1" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>892</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>893</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>896</v>
       </c>
-      <c r="B1" s="19" t="s">
-        <v>893</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>894</v>
-      </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
+        <v>885</v>
+      </c>
+      <c r="F1" s="19" t="s">
         <v>897</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>886</v>
       </c>
-      <c r="F1" s="19" t="s">
-        <v>898</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>3</v>
       </c>
@@ -5287,7 +5291,7 @@
       </c>
       <c r="G2" s="20"/>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>3</v>
       </c>
@@ -5308,7 +5312,7 @@
       </c>
       <c r="G3" s="20"/>
     </row>
-    <row r="4" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
         <v>3</v>
       </c>
@@ -5329,7 +5333,7 @@
       </c>
       <c r="G4" s="20"/>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
         <v>3</v>
       </c>
@@ -5346,11 +5350,11 @@
         <v>1</v>
       </c>
       <c r="F5" s="22">
-        <v>1600000</v>
+        <v>1100000</v>
       </c>
       <c r="G5" s="20"/>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
         <v>3</v>
       </c>
@@ -5367,11 +5371,11 @@
         <v>1</v>
       </c>
       <c r="F6" s="22">
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="G6" s="20"/>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
         <v>3</v>
       </c>
@@ -5392,7 +5396,7 @@
       </c>
       <c r="G7" s="20"/>
     </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
         <v>3</v>
       </c>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="G8" s="20"/>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="20" t="s">
         <v>3</v>
       </c>
@@ -5434,7 +5438,7 @@
       </c>
       <c r="G9" s="20"/>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
         <v>3</v>
       </c>
@@ -5455,7 +5459,7 @@
       </c>
       <c r="G10" s="20"/>
     </row>
-    <row r="11" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="20" t="s">
         <v>3</v>
       </c>
@@ -5476,7 +5480,7 @@
       </c>
       <c r="G11" s="20"/>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
         <v>3</v>
       </c>
@@ -5493,11 +5497,11 @@
         <v>1</v>
       </c>
       <c r="F12" s="22">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="G12" s="20"/>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="20" t="s">
         <v>3</v>
       </c>
@@ -5518,7 +5522,7 @@
       </c>
       <c r="G13" s="20"/>
     </row>
-    <row r="14" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="20" t="s">
         <v>3</v>
       </c>
@@ -5539,7 +5543,7 @@
       </c>
       <c r="G14" s="20"/>
     </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="20" t="s">
         <v>3</v>
       </c>
@@ -5560,7 +5564,7 @@
       </c>
       <c r="G15" s="20"/>
     </row>
-    <row r="16" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="20" t="s">
         <v>3</v>
       </c>
@@ -5581,7 +5585,7 @@
       </c>
       <c r="G16" s="20"/>
     </row>
-    <row r="17" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
         <v>3</v>
       </c>
@@ -5602,7 +5606,7 @@
       </c>
       <c r="G17" s="20"/>
     </row>
-    <row r="18" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="20" t="s">
         <v>3</v>
       </c>
@@ -5623,7 +5627,7 @@
       </c>
       <c r="G18" s="20"/>
     </row>
-    <row r="19" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="20" t="s">
         <v>3</v>
       </c>
@@ -5644,7 +5648,7 @@
       </c>
       <c r="G19" s="20"/>
     </row>
-    <row r="20" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="20" t="s">
         <v>3</v>
       </c>
@@ -5665,7 +5669,7 @@
       </c>
       <c r="G20" s="20"/>
     </row>
-    <row r="21" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="20" t="s">
         <v>3</v>
       </c>
@@ -5676,7 +5680,7 @@
         <v>712</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E21" s="20">
         <v>1</v>
@@ -5686,7 +5690,7 @@
       </c>
       <c r="G21" s="20"/>
     </row>
-    <row r="22" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
         <v>3</v>
       </c>
@@ -5707,7 +5711,7 @@
       </c>
       <c r="G22" s="20"/>
     </row>
-    <row r="23" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="20" t="s">
         <v>3</v>
       </c>
@@ -5726,7 +5730,7 @@
       <c r="F23" s="22"/>
       <c r="G23" s="20"/>
     </row>
-    <row r="24" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="20" t="s">
         <v>3</v>
       </c>
@@ -5745,18 +5749,18 @@
       <c r="F24" s="22"/>
       <c r="G24" s="20"/>
     </row>
-    <row r="25" spans="1:7" s="1" customFormat="1" ht="258.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="20" t="s">
+        <v>834</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>835</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>836</v>
-      </c>
       <c r="C25" s="20" t="s">
-        <v>749</v>
+        <v>996</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E25" s="20">
         <v>1</v>
@@ -5766,18 +5770,18 @@
       </c>
       <c r="G25" s="20"/>
     </row>
-    <row r="26" spans="1:7" s="1" customFormat="1" ht="184.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="20" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D26" s="21" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E26" s="20">
         <v>1</v>
@@ -5787,18 +5791,18 @@
       </c>
       <c r="G26" s="20"/>
     </row>
-    <row r="27" spans="1:7" s="1" customFormat="1" ht="184.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="20" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D27" s="21" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E27" s="20">
         <v>1</v>
@@ -5808,18 +5812,18 @@
       </c>
       <c r="G27" s="20"/>
     </row>
-    <row r="28" spans="1:7" s="1" customFormat="1" ht="184.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="20" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D28" s="21" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E28" s="20">
         <v>1</v>
@@ -5829,18 +5833,18 @@
       </c>
       <c r="G28" s="20"/>
     </row>
-    <row r="29" spans="1:7" s="1" customFormat="1" ht="184.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="20" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D29" s="21" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E29" s="20">
         <v>1</v>
@@ -5850,7 +5854,7 @@
       </c>
       <c r="G29" s="20"/>
     </row>
-    <row r="30" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="20" t="s">
         <v>53</v>
       </c>
@@ -5861,7 +5865,7 @@
         <v>647</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E30" s="20">
         <v>1</v>
@@ -5871,7 +5875,7 @@
       </c>
       <c r="G30" s="20"/>
     </row>
-    <row r="31" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="20" t="s">
         <v>53</v>
       </c>
@@ -5879,7 +5883,7 @@
         <v>648</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D31" s="21" t="s">
         <v>44</v>
@@ -5892,7 +5896,7 @@
       </c>
       <c r="G31" s="20"/>
     </row>
-    <row r="32" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="20" t="s">
         <v>53</v>
       </c>
@@ -5900,10 +5904,10 @@
         <v>649</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D32" s="21" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E32" s="20">
         <v>1</v>
@@ -5913,7 +5917,7 @@
       </c>
       <c r="G32" s="20"/>
     </row>
-    <row r="33" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
         <v>53</v>
       </c>
@@ -5924,7 +5928,7 @@
         <v>651</v>
       </c>
       <c r="D33" s="21" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E33" s="20">
         <v>1</v>
@@ -5934,7 +5938,7 @@
       </c>
       <c r="G33" s="20"/>
     </row>
-    <row r="34" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="20" t="s">
         <v>53</v>
       </c>
@@ -5945,7 +5949,7 @@
         <v>653</v>
       </c>
       <c r="D34" s="21" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E34" s="20">
         <v>1</v>
@@ -5955,7 +5959,7 @@
       </c>
       <c r="G34" s="20"/>
     </row>
-    <row r="35" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="20" t="s">
         <v>53</v>
       </c>
@@ -5966,7 +5970,7 @@
         <v>655</v>
       </c>
       <c r="D35" s="21" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E35" s="20">
         <v>1</v>
@@ -5976,18 +5980,18 @@
       </c>
       <c r="G35" s="20"/>
     </row>
-    <row r="36" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="20" t="s">
         <v>53</v>
       </c>
       <c r="B36" s="20" t="s">
+        <v>823</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>825</v>
+      </c>
+      <c r="D36" s="21" t="s">
         <v>824</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>826</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>825</v>
       </c>
       <c r="E36" s="20">
         <v>1</v>
@@ -5997,7 +6001,7 @@
       </c>
       <c r="G36" s="20"/>
     </row>
-    <row r="37" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="20" t="s">
         <v>619</v>
       </c>
@@ -6005,10 +6009,10 @@
         <v>6</v>
       </c>
       <c r="C37" s="20" t="s">
+        <v>756</v>
+      </c>
+      <c r="D37" s="21" t="s">
         <v>757</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>758</v>
       </c>
       <c r="E37" s="20">
         <v>1</v>
@@ -6018,7 +6022,7 @@
       </c>
       <c r="G37" s="20"/>
     </row>
-    <row r="38" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="20" t="s">
         <v>619</v>
       </c>
@@ -6026,10 +6030,10 @@
         <v>7</v>
       </c>
       <c r="C38" s="20" t="s">
+        <v>758</v>
+      </c>
+      <c r="D38" s="21" t="s">
         <v>759</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>760</v>
       </c>
       <c r="E38" s="20">
         <v>1</v>
@@ -6039,7 +6043,7 @@
       </c>
       <c r="G38" s="20"/>
     </row>
-    <row r="39" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="20" t="s">
         <v>619</v>
       </c>
@@ -6050,7 +6054,7 @@
         <v>714</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E39" s="20">
         <v>1</v>
@@ -6060,7 +6064,7 @@
       </c>
       <c r="G39" s="20"/>
     </row>
-    <row r="40" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="20" t="s">
         <v>619</v>
       </c>
@@ -6068,10 +6072,10 @@
         <v>657</v>
       </c>
       <c r="C40" s="20" t="s">
+        <v>761</v>
+      </c>
+      <c r="D40" s="21" t="s">
         <v>762</v>
-      </c>
-      <c r="D40" s="21" t="s">
-        <v>763</v>
       </c>
       <c r="E40" s="20">
         <v>1</v>
@@ -6081,7 +6085,7 @@
       </c>
       <c r="G40" s="20"/>
     </row>
-    <row r="41" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="20" t="s">
         <v>619</v>
       </c>
@@ -6089,10 +6093,10 @@
         <v>658</v>
       </c>
       <c r="C41" s="20" t="s">
+        <v>763</v>
+      </c>
+      <c r="D41" s="21" t="s">
         <v>764</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>765</v>
       </c>
       <c r="E41" s="20">
         <v>1</v>
@@ -6102,7 +6106,7 @@
       </c>
       <c r="G41" s="20"/>
     </row>
-    <row r="42" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="20" t="s">
         <v>619</v>
       </c>
@@ -6110,10 +6114,10 @@
         <v>659</v>
       </c>
       <c r="C42" s="20" t="s">
+        <v>765</v>
+      </c>
+      <c r="D42" s="21" t="s">
         <v>766</v>
-      </c>
-      <c r="D42" s="21" t="s">
-        <v>767</v>
       </c>
       <c r="E42" s="20">
         <v>1</v>
@@ -6123,7 +6127,7 @@
       </c>
       <c r="G42" s="20"/>
     </row>
-    <row r="43" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="20" t="s">
         <v>619</v>
       </c>
@@ -6134,7 +6138,7 @@
         <v>705</v>
       </c>
       <c r="D43" s="21" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E43" s="20">
         <v>1</v>
@@ -6144,7 +6148,7 @@
       </c>
       <c r="G43" s="20"/>
     </row>
-    <row r="44" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="20" t="s">
         <v>619</v>
       </c>
@@ -6155,7 +6159,7 @@
         <v>12</v>
       </c>
       <c r="D44" s="21" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="E44" s="20">
         <v>1</v>
@@ -6165,7 +6169,7 @@
       </c>
       <c r="G44" s="20"/>
     </row>
-    <row r="45" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="20" t="s">
         <v>619</v>
       </c>
@@ -6173,10 +6177,10 @@
         <v>662</v>
       </c>
       <c r="C45" s="20" t="s">
+        <v>769</v>
+      </c>
+      <c r="D45" s="21" t="s">
         <v>770</v>
-      </c>
-      <c r="D45" s="21" t="s">
-        <v>771</v>
       </c>
       <c r="E45" s="20">
         <v>1</v>
@@ -6186,7 +6190,7 @@
       </c>
       <c r="G45" s="20"/>
     </row>
-    <row r="46" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="20" t="s">
         <v>619</v>
       </c>
@@ -6194,10 +6198,10 @@
         <v>663</v>
       </c>
       <c r="C46" s="20" t="s">
+        <v>771</v>
+      </c>
+      <c r="D46" s="21" t="s">
         <v>772</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>773</v>
       </c>
       <c r="E46" s="20">
         <v>1</v>
@@ -6207,7 +6211,7 @@
       </c>
       <c r="G46" s="20"/>
     </row>
-    <row r="47" spans="1:7" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="20" t="s">
         <v>619</v>
       </c>
@@ -6228,7 +6232,7 @@
       </c>
       <c r="G47" s="20"/>
     </row>
-    <row r="48" spans="1:7" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="20" t="s">
         <v>619</v>
       </c>
@@ -6249,7 +6253,7 @@
       </c>
       <c r="G48" s="20"/>
     </row>
-    <row r="49" spans="1:7" s="4" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" s="4" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="20" t="s">
         <v>619</v>
       </c>
@@ -6270,7 +6274,7 @@
       </c>
       <c r="G49" s="20"/>
     </row>
-    <row r="50" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="20" t="s">
         <v>619</v>
       </c>
@@ -6281,17 +6285,17 @@
         <v>711</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E50" s="20">
         <v>1</v>
       </c>
       <c r="F50" s="22">
-        <v>100000</v>
+        <v>200000</v>
       </c>
       <c r="G50" s="20"/>
     </row>
-    <row r="51" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="20" t="s">
         <v>619</v>
       </c>
@@ -6302,7 +6306,7 @@
         <v>717</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="E51" s="20">
         <v>1</v>
@@ -6312,7 +6316,7 @@
       </c>
       <c r="G51" s="20"/>
     </row>
-    <row r="52" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="20" t="s">
         <v>619</v>
       </c>
@@ -6323,7 +6327,7 @@
         <v>712</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E52" s="20">
         <v>1</v>
@@ -6333,18 +6337,18 @@
       </c>
       <c r="G52" s="20"/>
     </row>
-    <row r="53" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="20" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B53" s="20" t="s">
         <v>669</v>
       </c>
       <c r="C53" s="20" t="s">
+        <v>777</v>
+      </c>
+      <c r="D53" s="21" t="s">
         <v>778</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>779</v>
       </c>
       <c r="E53" s="20">
         <v>1</v>
@@ -6354,18 +6358,18 @@
       </c>
       <c r="G53" s="20"/>
     </row>
-    <row r="54" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="20" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B54" s="20" t="s">
         <v>670</v>
       </c>
       <c r="C54" s="20" t="s">
+        <v>779</v>
+      </c>
+      <c r="D54" s="21" t="s">
         <v>780</v>
-      </c>
-      <c r="D54" s="21" t="s">
-        <v>781</v>
       </c>
       <c r="E54" s="20">
         <v>1</v>
@@ -6375,18 +6379,18 @@
       </c>
       <c r="G54" s="20"/>
     </row>
-    <row r="55" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="20" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B55" s="20" t="s">
         <v>671</v>
       </c>
       <c r="C55" s="20" t="s">
+        <v>781</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>782</v>
-      </c>
-      <c r="D55" s="21" t="s">
-        <v>783</v>
       </c>
       <c r="E55" s="20">
         <v>1</v>
@@ -6396,18 +6400,18 @@
       </c>
       <c r="G55" s="20"/>
     </row>
-    <row r="56" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="20" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B56" s="20" t="s">
         <v>672</v>
       </c>
       <c r="C56" s="20" t="s">
+        <v>783</v>
+      </c>
+      <c r="D56" s="21" t="s">
         <v>784</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>785</v>
       </c>
       <c r="E56" s="20">
         <v>1</v>
@@ -6417,7 +6421,7 @@
       </c>
       <c r="G56" s="20"/>
     </row>
-    <row r="57" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="20" t="s">
         <v>54</v>
       </c>
@@ -6428,7 +6432,7 @@
         <v>715</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E57" s="20">
         <v>1</v>
@@ -6438,7 +6442,7 @@
       </c>
       <c r="G57" s="20"/>
     </row>
-    <row r="58" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="20" t="s">
         <v>54</v>
       </c>
@@ -6446,10 +6450,10 @@
         <v>674</v>
       </c>
       <c r="C58" s="20" t="s">
+        <v>786</v>
+      </c>
+      <c r="D58" s="21" t="s">
         <v>787</v>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>788</v>
       </c>
       <c r="E58" s="20">
         <v>1</v>
@@ -6459,7 +6463,7 @@
       </c>
       <c r="G58" s="20"/>
     </row>
-    <row r="59" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="20" t="s">
         <v>54</v>
       </c>
@@ -6467,10 +6471,10 @@
         <v>675</v>
       </c>
       <c r="C59" s="20" t="s">
+        <v>788</v>
+      </c>
+      <c r="D59" s="21" t="s">
         <v>789</v>
-      </c>
-      <c r="D59" s="21" t="s">
-        <v>790</v>
       </c>
       <c r="E59" s="20">
         <v>1</v>
@@ -6480,7 +6484,7 @@
       </c>
       <c r="G59" s="20"/>
     </row>
-    <row r="60" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="20" t="s">
         <v>54</v>
       </c>
@@ -6488,10 +6492,10 @@
         <v>676</v>
       </c>
       <c r="C60" s="20" t="s">
+        <v>790</v>
+      </c>
+      <c r="D60" s="21" t="s">
         <v>791</v>
-      </c>
-      <c r="D60" s="21" t="s">
-        <v>792</v>
       </c>
       <c r="E60" s="20">
         <v>1</v>
@@ -6501,7 +6505,7 @@
       </c>
       <c r="G60" s="20"/>
     </row>
-    <row r="61" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="20" t="s">
         <v>54</v>
       </c>
@@ -6509,10 +6513,10 @@
         <v>677</v>
       </c>
       <c r="C61" s="20" t="s">
+        <v>792</v>
+      </c>
+      <c r="D61" s="21" t="s">
         <v>793</v>
-      </c>
-      <c r="D61" s="21" t="s">
-        <v>794</v>
       </c>
       <c r="E61" s="20">
         <v>1</v>
@@ -6522,7 +6526,7 @@
       </c>
       <c r="G61" s="20"/>
     </row>
-    <row r="62" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="20" t="s">
         <v>54</v>
       </c>
@@ -6530,10 +6534,10 @@
         <v>678</v>
       </c>
       <c r="C62" s="20" t="s">
+        <v>794</v>
+      </c>
+      <c r="D62" s="21" t="s">
         <v>795</v>
-      </c>
-      <c r="D62" s="21" t="s">
-        <v>796</v>
       </c>
       <c r="E62" s="20">
         <v>1</v>
@@ -6543,7 +6547,7 @@
       </c>
       <c r="G62" s="20"/>
     </row>
-    <row r="63" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="20" t="s">
         <v>54</v>
       </c>
@@ -6554,7 +6558,7 @@
         <v>680</v>
       </c>
       <c r="D63" s="21" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E63" s="20">
         <v>1</v>
@@ -6564,7 +6568,7 @@
       </c>
       <c r="G63" s="20"/>
     </row>
-    <row r="64" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="20" t="s">
         <v>54</v>
       </c>
@@ -6575,7 +6579,7 @@
         <v>681</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E64" s="20">
         <v>1</v>
@@ -6585,18 +6589,18 @@
       </c>
       <c r="G64" s="20"/>
     </row>
-    <row r="65" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="20" t="s">
+        <v>978</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>976</v>
+      </c>
+      <c r="C65" s="20" t="s">
         <v>979</v>
       </c>
-      <c r="B65" s="20" t="s">
-        <v>977</v>
-      </c>
-      <c r="C65" s="20" t="s">
+      <c r="D65" s="21" t="s">
         <v>980</v>
-      </c>
-      <c r="D65" s="21" t="s">
-        <v>981</v>
       </c>
       <c r="E65" s="20">
         <v>1</v>
@@ -6606,18 +6610,18 @@
       </c>
       <c r="G65" s="20"/>
     </row>
-    <row r="66" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="20" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="C66" s="20" t="s">
+        <v>981</v>
+      </c>
+      <c r="D66" s="21" t="s">
         <v>982</v>
-      </c>
-      <c r="D66" s="21" t="s">
-        <v>983</v>
       </c>
       <c r="E66" s="20">
         <v>1</v>
@@ -6627,7 +6631,7 @@
       </c>
       <c r="G66" s="20"/>
     </row>
-    <row r="67" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="20" t="s">
         <v>56</v>
       </c>
@@ -6638,7 +6642,7 @@
         <v>18</v>
       </c>
       <c r="D67" s="21" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E67" s="20">
         <v>1</v>
@@ -6648,7 +6652,7 @@
       </c>
       <c r="G67" s="20"/>
     </row>
-    <row r="68" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="20" t="s">
         <v>56</v>
       </c>
@@ -6659,7 +6663,7 @@
         <v>18</v>
       </c>
       <c r="D68" s="21" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E68" s="20">
         <v>1</v>
@@ -6668,10 +6672,10 @@
         <v>500000</v>
       </c>
       <c r="G68" s="20" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="20" t="s">
         <v>56</v>
       </c>
@@ -6679,10 +6683,10 @@
         <v>682</v>
       </c>
       <c r="C69" s="20" t="s">
+        <v>799</v>
+      </c>
+      <c r="D69" s="21" t="s">
         <v>800</v>
-      </c>
-      <c r="D69" s="21" t="s">
-        <v>801</v>
       </c>
       <c r="E69" s="20">
         <v>1</v>
@@ -6692,7 +6696,7 @@
       </c>
       <c r="G69" s="20"/>
     </row>
-    <row r="70" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="20" t="s">
         <v>56</v>
       </c>
@@ -6700,10 +6704,10 @@
         <v>683</v>
       </c>
       <c r="C70" s="20" t="s">
+        <v>801</v>
+      </c>
+      <c r="D70" s="21" t="s">
         <v>802</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>803</v>
       </c>
       <c r="E70" s="20">
         <v>1</v>
@@ -6713,7 +6717,7 @@
       </c>
       <c r="G70" s="20"/>
     </row>
-    <row r="71" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="20" t="s">
         <v>56</v>
       </c>
@@ -6724,17 +6728,17 @@
         <v>711</v>
       </c>
       <c r="D71" s="21" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E71" s="20">
         <v>1</v>
       </c>
       <c r="F71" s="22">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="G71" s="20"/>
     </row>
-    <row r="72" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="27" t="s">
         <v>10</v>
       </c>
@@ -6745,7 +6749,7 @@
         <v>720</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E72" s="27">
         <v>1</v>
@@ -6755,7 +6759,7 @@
       </c>
       <c r="G72" s="27"/>
     </row>
-    <row r="73" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="27" t="s">
         <v>10</v>
       </c>
@@ -6763,7 +6767,7 @@
         <v>685</v>
       </c>
       <c r="C73" s="27" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D73" s="28" t="s">
         <v>686</v>
@@ -6776,7 +6780,7 @@
       </c>
       <c r="G73" s="27"/>
     </row>
-    <row r="74" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="27" t="s">
         <v>10</v>
       </c>
@@ -6784,7 +6788,7 @@
         <v>687</v>
       </c>
       <c r="C74" s="27" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D74" s="28" t="s">
         <v>688</v>
@@ -6797,7 +6801,7 @@
       </c>
       <c r="G74" s="27"/>
     </row>
-    <row r="75" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="27" t="s">
         <v>10</v>
       </c>
@@ -6805,7 +6809,7 @@
         <v>689</v>
       </c>
       <c r="C75" s="27" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D75" s="28" t="s">
         <v>690</v>
@@ -6818,7 +6822,7 @@
       </c>
       <c r="G75" s="27"/>
     </row>
-    <row r="76" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="27" t="s">
         <v>10</v>
       </c>
@@ -6826,7 +6830,7 @@
         <v>691</v>
       </c>
       <c r="C76" s="27" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D76" s="28" t="s">
         <v>692</v>
@@ -6839,7 +6843,7 @@
       </c>
       <c r="G76" s="27"/>
     </row>
-    <row r="77" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="27" t="s">
         <v>10</v>
       </c>
@@ -6847,7 +6851,7 @@
         <v>693</v>
       </c>
       <c r="C77" s="27" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D77" s="28" t="s">
         <v>692</v>
@@ -6860,7 +6864,7 @@
       </c>
       <c r="G77" s="27"/>
     </row>
-    <row r="78" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="27" t="s">
         <v>10</v>
       </c>
@@ -6868,10 +6872,10 @@
         <v>694</v>
       </c>
       <c r="C78" s="27" t="s">
+        <v>809</v>
+      </c>
+      <c r="D78" s="28" t="s">
         <v>810</v>
-      </c>
-      <c r="D78" s="28" t="s">
-        <v>811</v>
       </c>
       <c r="E78" s="27">
         <v>1</v>
@@ -6881,7 +6885,7 @@
       </c>
       <c r="G78" s="27"/>
     </row>
-    <row r="79" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="27" t="s">
         <v>10</v>
       </c>
@@ -6889,7 +6893,7 @@
         <v>695</v>
       </c>
       <c r="C79" s="27" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D79" s="28" t="s">
         <v>696</v>
@@ -6902,7 +6906,7 @@
       </c>
       <c r="G79" s="27"/>
     </row>
-    <row r="80" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="27" t="s">
         <v>10</v>
       </c>
@@ -6910,7 +6914,7 @@
         <v>697</v>
       </c>
       <c r="C80" s="27" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="D80" s="28" t="s">
         <v>698</v>
@@ -6923,7 +6927,7 @@
       </c>
       <c r="G80" s="27"/>
     </row>
-    <row r="81" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="27" t="s">
         <v>10</v>
       </c>
@@ -6944,7 +6948,7 @@
       </c>
       <c r="G81" s="27"/>
     </row>
-    <row r="82" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="27" t="s">
         <v>10</v>
       </c>
@@ -6955,7 +6959,7 @@
         <v>24</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E82" s="27">
         <v>1</v>
@@ -6965,7 +6969,7 @@
       </c>
       <c r="G82" s="27"/>
     </row>
-    <row r="83" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="30" t="s">
         <v>38</v>
       </c>
@@ -6973,10 +6977,10 @@
         <v>40</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="D83" s="31" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E83" s="30">
         <v>1</v>
@@ -6985,10 +6989,10 @@
         <v>2000000</v>
       </c>
       <c r="G83" s="33" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="30" t="s">
         <v>38</v>
       </c>
@@ -6999,7 +7003,7 @@
         <v>39</v>
       </c>
       <c r="D84" s="31" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E84" s="30">
         <v>1</v>
@@ -7009,7 +7013,7 @@
       </c>
       <c r="G84" s="30"/>
     </row>
-    <row r="85" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="30" t="s">
         <v>38</v>
       </c>
@@ -7017,10 +7021,10 @@
         <v>703</v>
       </c>
       <c r="C85" s="30" t="s">
+        <v>816</v>
+      </c>
+      <c r="D85" s="31" t="s">
         <v>817</v>
-      </c>
-      <c r="D85" s="31" t="s">
-        <v>818</v>
       </c>
       <c r="E85" s="30">
         <v>1</v>
@@ -7029,10 +7033,10 @@
         <v>70000</v>
       </c>
       <c r="G85" s="30" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="30" t="s">
         <v>38</v>
       </c>
@@ -7040,10 +7044,10 @@
         <v>41</v>
       </c>
       <c r="C86" s="30" t="s">
+        <v>818</v>
+      </c>
+      <c r="D86" s="31" t="s">
         <v>819</v>
-      </c>
-      <c r="D86" s="31" t="s">
-        <v>820</v>
       </c>
       <c r="E86" s="30">
         <v>1</v>
@@ -7053,12 +7057,12 @@
       </c>
       <c r="G86" s="30"/>
     </row>
-    <row r="87" spans="1:7" s="1" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="20" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C87" s="20" t="s">
         <v>59</v>
@@ -7074,18 +7078,18 @@
       </c>
       <c r="G87" s="26"/>
     </row>
-    <row r="88" spans="1:7" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="20" t="s">
+        <v>830</v>
+      </c>
+      <c r="B88" s="20" t="s">
         <v>831</v>
       </c>
-      <c r="B88" s="20" t="s">
+      <c r="C88" s="20" t="s">
         <v>832</v>
       </c>
-      <c r="C88" s="20" t="s">
+      <c r="D88" s="21" t="s">
         <v>833</v>
-      </c>
-      <c r="D88" s="21" t="s">
-        <v>834</v>
       </c>
       <c r="E88" s="20">
         <v>1</v>
@@ -7117,22 +7121,22 @@
   <sheetData>
     <row r="1" spans="1:9" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
+        <v>891</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>892</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="19" t="s">
         <v>893</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="19" t="s">
+        <v>885</v>
+      </c>
+      <c r="E1" s="19" t="s">
         <v>894</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>886</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>895</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>887</v>
       </c>
       <c r="G1" s="19"/>
       <c r="H1"/>
@@ -7707,16 +7711,16 @@
     </row>
     <row r="33" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B33" s="35" t="s">
+        <v>847</v>
+      </c>
+      <c r="C33" s="35" t="s">
         <v>848</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="D33" s="35" t="s">
         <v>849</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>850</v>
       </c>
       <c r="E33" s="36">
         <v>1</v>
@@ -7725,13 +7729,13 @@
     </row>
     <row r="34" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B34" s="35" t="s">
+        <v>850</v>
+      </c>
+      <c r="C34" s="35" t="s">
         <v>851</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>852</v>
       </c>
       <c r="D34" s="35" t="s">
         <v>0</v>
@@ -7743,16 +7747,16 @@
     </row>
     <row r="35" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B35" s="35" t="s">
+        <v>852</v>
+      </c>
+      <c r="C35" s="35" t="s">
         <v>853</v>
       </c>
-      <c r="C35" s="35" t="s">
-        <v>854</v>
-      </c>
       <c r="D35" s="35" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E35" s="36">
         <v>1</v>
@@ -7761,16 +7765,16 @@
     </row>
     <row r="36" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B36" s="35" t="s">
+        <v>854</v>
+      </c>
+      <c r="C36" s="35" t="s">
         <v>855</v>
       </c>
-      <c r="C36" s="35" t="s">
-        <v>856</v>
-      </c>
       <c r="D36" s="35" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E36" s="36">
         <v>1</v>
@@ -7779,13 +7783,13 @@
     </row>
     <row r="37" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B37" s="35" t="s">
+        <v>856</v>
+      </c>
+      <c r="C37" s="35" t="s">
         <v>857</v>
-      </c>
-      <c r="C37" s="35" t="s">
-        <v>858</v>
       </c>
       <c r="D37" s="35" t="s">
         <v>0</v>
@@ -7797,13 +7801,13 @@
     </row>
     <row r="38" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B38" s="35" t="s">
+        <v>858</v>
+      </c>
+      <c r="C38" s="35" t="s">
         <v>859</v>
-      </c>
-      <c r="C38" s="35" t="s">
-        <v>860</v>
       </c>
       <c r="D38" s="35" t="s">
         <v>0</v>
@@ -7815,13 +7819,13 @@
     </row>
     <row r="39" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B39" s="35" t="s">
+        <v>860</v>
+      </c>
+      <c r="C39" s="35" t="s">
         <v>861</v>
-      </c>
-      <c r="C39" s="35" t="s">
-        <v>862</v>
       </c>
       <c r="D39" s="35" t="s">
         <v>0</v>
@@ -7833,13 +7837,13 @@
     </row>
     <row r="40" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B40" s="35" t="s">
+        <v>862</v>
+      </c>
+      <c r="C40" s="35" t="s">
         <v>863</v>
-      </c>
-      <c r="C40" s="35" t="s">
-        <v>864</v>
       </c>
       <c r="D40" s="35" t="s">
         <v>0</v>
@@ -7851,13 +7855,13 @@
     </row>
     <row r="41" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B41" s="35" t="s">
+        <v>864</v>
+      </c>
+      <c r="C41" s="35" t="s">
         <v>865</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>866</v>
       </c>
       <c r="D41" s="35" t="s">
         <v>0</v>
@@ -7869,16 +7873,16 @@
     </row>
     <row r="42" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B42" s="35" t="s">
+        <v>866</v>
+      </c>
+      <c r="C42" s="35" t="s">
         <v>867</v>
       </c>
-      <c r="C42" s="35" t="s">
-        <v>868</v>
-      </c>
       <c r="D42" s="35" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E42" s="36">
         <v>1</v>
@@ -7887,16 +7891,16 @@
     </row>
     <row r="43" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B43" s="35" t="s">
+        <v>868</v>
+      </c>
+      <c r="C43" s="35" t="s">
         <v>869</v>
       </c>
-      <c r="C43" s="35" t="s">
-        <v>870</v>
-      </c>
       <c r="D43" s="35" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E43" s="36">
         <v>1</v>
@@ -7905,16 +7909,16 @@
     </row>
     <row r="44" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B44" s="35" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>880</v>
+        <v>997</v>
       </c>
       <c r="D44" s="35" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E44" s="35">
         <v>1</v>
@@ -7923,16 +7927,16 @@
     </row>
     <row r="45" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B45" s="35" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E45" s="35">
         <v>1</v>
@@ -7941,13 +7945,13 @@
     </row>
     <row r="46" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B46" s="35" t="s">
+        <v>870</v>
+      </c>
+      <c r="C46" s="35" t="s">
         <v>871</v>
-      </c>
-      <c r="C46" s="35" t="s">
-        <v>872</v>
       </c>
       <c r="D46" s="35" t="s">
         <v>0</v>
@@ -7959,13 +7963,13 @@
     </row>
     <row r="47" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B47" s="35" t="s">
+        <v>872</v>
+      </c>
+      <c r="C47" s="35" t="s">
         <v>873</v>
-      </c>
-      <c r="C47" s="35" t="s">
-        <v>874</v>
       </c>
       <c r="D47" s="35" t="s">
         <v>0</v>
@@ -7977,16 +7981,16 @@
     </row>
     <row r="48" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B48" s="35" t="s">
+        <v>874</v>
+      </c>
+      <c r="C48" s="35" t="s">
         <v>875</v>
       </c>
-      <c r="C48" s="35" t="s">
-        <v>876</v>
-      </c>
       <c r="D48" s="35" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E48" s="36">
         <v>1</v>
@@ -7995,16 +7999,16 @@
     </row>
     <row r="49" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="35" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B49" s="35" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C49" s="35" t="s">
         <v>453</v>
       </c>
       <c r="D49" s="35" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E49" s="36">
         <v>1</v>
@@ -8016,7 +8020,7 @@
         <v>60</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C50" s="18" t="s">
         <v>59</v>
@@ -8065,10 +8069,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8076,7 +8080,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="3" spans="1:2" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -8105,10 +8109,10 @@
     </row>
     <row r="6" spans="1:2" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>882</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>883</v>
       </c>
     </row>
   </sheetData>
@@ -8138,34 +8142,34 @@
   <sheetData>
     <row r="1" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
+        <v>887</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>888</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="19" t="s">
+        <v>898</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>902</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>893</v>
+      </c>
+      <c r="F1" s="19" t="s">
         <v>889</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>899</v>
-      </c>
-      <c r="D1" s="19" t="s">
+      <c r="G1" s="19" t="s">
+        <v>884</v>
+      </c>
+      <c r="H1" s="19" t="s">
         <v>903</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>894</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>890</v>
-      </c>
-      <c r="G1" s="19" t="s">
-        <v>885</v>
-      </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>904</v>
       </c>
-      <c r="I1" s="19" t="s">
-        <v>905</v>
-      </c>
       <c r="J1" s="19" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="17" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
@@ -8173,7 +8177,7 @@
         <v>444</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>114</v>
@@ -8185,7 +8189,7 @@
         <v>445</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G2" s="41" t="s">
         <v>585</v>
@@ -8203,7 +8207,7 @@
         <v>444</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C3" s="20" t="s">
         <v>114</v>
@@ -8233,7 +8237,7 @@
         <v>444</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>114</v>
@@ -8263,7 +8267,7 @@
         <v>444</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C5" s="20" t="s">
         <v>114</v>
@@ -8293,7 +8297,7 @@
         <v>444</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>114</v>
@@ -8323,7 +8327,7 @@
         <v>444</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>114</v>
@@ -8353,7 +8357,7 @@
         <v>444</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>114</v>
@@ -8383,7 +8387,7 @@
         <v>444</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>114</v>
@@ -8413,7 +8417,7 @@
         <v>444</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>114</v>
@@ -8443,7 +8447,7 @@
         <v>444</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>128</v>
@@ -8473,7 +8477,7 @@
         <v>444</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>128</v>
@@ -8503,7 +8507,7 @@
         <v>600</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>133</v>
@@ -8533,7 +8537,7 @@
         <v>600</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>133</v>
@@ -8563,7 +8567,7 @@
         <v>600</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>133</v>
@@ -8593,7 +8597,7 @@
         <v>600</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>133</v>
@@ -8623,7 +8627,7 @@
         <v>600</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>133</v>
@@ -8653,7 +8657,7 @@
         <v>600</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>133</v>
@@ -8683,7 +8687,7 @@
         <v>600</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>133</v>
@@ -8713,7 +8717,7 @@
         <v>600</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>133</v>
@@ -8743,7 +8747,7 @@
         <v>600</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>133</v>
@@ -8773,7 +8777,7 @@
         <v>600</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>133</v>
@@ -8803,7 +8807,7 @@
         <v>600</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>133</v>
@@ -8833,7 +8837,7 @@
         <v>600</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>154</v>
@@ -8863,7 +8867,7 @@
         <v>600</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>154</v>
@@ -8893,7 +8897,7 @@
         <v>600</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C26" s="20" t="s">
         <v>154</v>
@@ -8923,7 +8927,7 @@
         <v>600</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>154</v>
@@ -8953,7 +8957,7 @@
         <v>600</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>154</v>
@@ -8983,7 +8987,7 @@
         <v>600</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>154</v>
@@ -9013,7 +9017,7 @@
         <v>600</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>154</v>
@@ -9043,7 +9047,7 @@
         <v>600</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>154</v>
@@ -9073,7 +9077,7 @@
         <v>600</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C32" s="20" t="s">
         <v>154</v>
@@ -9103,7 +9107,7 @@
         <v>600</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C33" s="20" t="s">
         <v>154</v>
@@ -9133,7 +9137,7 @@
         <v>600</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C34" s="20" t="s">
         <v>154</v>
@@ -9163,7 +9167,7 @@
         <v>600</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>154</v>
@@ -9193,7 +9197,7 @@
         <v>601</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>168</v>
@@ -9223,7 +9227,7 @@
         <v>601</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>168</v>
@@ -9253,7 +9257,7 @@
         <v>601</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C38" s="20" t="s">
         <v>168</v>
@@ -9283,7 +9287,7 @@
         <v>601</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>168</v>
@@ -9313,7 +9317,7 @@
         <v>601</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C40" s="20" t="s">
         <v>168</v>
@@ -9343,7 +9347,7 @@
         <v>601</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C41" s="20" t="s">
         <v>168</v>
@@ -9373,7 +9377,7 @@
         <v>601</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C42" s="20" t="s">
         <v>168</v>
@@ -9403,7 +9407,7 @@
         <v>601</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C43" s="20" t="s">
         <v>168</v>
@@ -9433,7 +9437,7 @@
         <v>601</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C44" s="20" t="s">
         <v>168</v>
@@ -9463,7 +9467,7 @@
         <v>601</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>168</v>
@@ -9493,7 +9497,7 @@
         <v>601</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C46" s="20" t="s">
         <v>168</v>
@@ -9523,7 +9527,7 @@
         <v>601</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C47" s="20" t="s">
         <v>168</v>
@@ -9553,7 +9557,7 @@
         <v>601</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C48" s="20" t="s">
         <v>168</v>
@@ -9583,7 +9587,7 @@
         <v>601</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C49" s="20" t="s">
         <v>191</v>
@@ -9613,7 +9617,7 @@
         <v>601</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C50" s="20" t="s">
         <v>191</v>
@@ -9643,7 +9647,7 @@
         <v>601</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C51" s="20" t="s">
         <v>191</v>
@@ -9673,7 +9677,7 @@
         <v>601</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C52" s="20" t="s">
         <v>191</v>
@@ -9703,7 +9707,7 @@
         <v>601</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C53" s="20" t="s">
         <v>191</v>
@@ -9733,7 +9737,7 @@
         <v>601</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C54" s="20" t="s">
         <v>191</v>
@@ -9763,7 +9767,7 @@
         <v>601</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C55" s="20" t="s">
         <v>191</v>
@@ -9793,7 +9797,7 @@
         <v>601</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C56" s="20" t="s">
         <v>191</v>
@@ -9823,7 +9827,7 @@
         <v>601</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C57" s="20" t="s">
         <v>191</v>
@@ -9853,7 +9857,7 @@
         <v>601</v>
       </c>
       <c r="B58" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C58" s="20" t="s">
         <v>191</v>
@@ -9883,7 +9887,7 @@
         <v>601</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C59" s="20" t="s">
         <v>191</v>
@@ -9913,7 +9917,7 @@
         <v>601</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>191</v>
@@ -9943,7 +9947,7 @@
         <v>601</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>191</v>
@@ -9973,7 +9977,7 @@
         <v>601</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C62" s="20" t="s">
         <v>191</v>
@@ -10003,7 +10007,7 @@
         <v>601</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C63" s="20" t="s">
         <v>191</v>
@@ -10033,7 +10037,7 @@
         <v>601</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C64" s="20" t="s">
         <v>191</v>
@@ -10063,7 +10067,7 @@
         <v>601</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C65" s="20" t="s">
         <v>191</v>
@@ -10093,7 +10097,7 @@
         <v>601</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C66" s="20" t="s">
         <v>191</v>
@@ -10123,7 +10127,7 @@
         <v>601</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C67" s="20" t="s">
         <v>191</v>
@@ -10153,7 +10157,7 @@
         <v>601</v>
       </c>
       <c r="B68" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C68" s="20" t="s">
         <v>191</v>
@@ -10183,7 +10187,7 @@
         <v>602</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C69" s="20" t="s">
         <v>218</v>
@@ -10213,7 +10217,7 @@
         <v>602</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C70" s="20" t="s">
         <v>218</v>
@@ -10243,7 +10247,7 @@
         <v>602</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C71" s="20" t="s">
         <v>218</v>
@@ -10273,7 +10277,7 @@
         <v>602</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C72" s="20" t="s">
         <v>218</v>
@@ -10303,7 +10307,7 @@
         <v>602</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C73" s="20" t="s">
         <v>218</v>
@@ -10333,7 +10337,7 @@
         <v>602</v>
       </c>
       <c r="B74" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C74" s="20" t="s">
         <v>218</v>
@@ -10363,7 +10367,7 @@
         <v>602</v>
       </c>
       <c r="B75" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>218</v>
@@ -10393,7 +10397,7 @@
         <v>602</v>
       </c>
       <c r="B76" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>218</v>
@@ -10423,7 +10427,7 @@
         <v>602</v>
       </c>
       <c r="B77" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>218</v>
@@ -10453,7 +10457,7 @@
         <v>602</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>218</v>
@@ -10483,7 +10487,7 @@
         <v>602</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>218</v>
@@ -10513,7 +10517,7 @@
         <v>602</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>218</v>
@@ -10543,7 +10547,7 @@
         <v>602</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>218</v>
@@ -10573,7 +10577,7 @@
         <v>602</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>218</v>
@@ -10603,7 +10607,7 @@
         <v>602</v>
       </c>
       <c r="B83" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>218</v>
@@ -10633,7 +10637,7 @@
         <v>602</v>
       </c>
       <c r="B84" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>218</v>
@@ -10663,7 +10667,7 @@
         <v>602</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C85" s="20" t="s">
         <v>218</v>
@@ -10693,7 +10697,7 @@
         <v>602</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C86" s="20" t="s">
         <v>218</v>
@@ -10723,7 +10727,7 @@
         <v>602</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C87" s="20" t="s">
         <v>218</v>
@@ -10753,7 +10757,7 @@
         <v>602</v>
       </c>
       <c r="B88" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C88" s="20" t="s">
         <v>218</v>
@@ -10783,7 +10787,7 @@
         <v>602</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C89" s="20" t="s">
         <v>218</v>
@@ -10813,7 +10817,7 @@
         <v>602</v>
       </c>
       <c r="B90" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C90" s="20" t="s">
         <v>218</v>
@@ -10843,7 +10847,7 @@
         <v>602</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="C91" s="20" t="s">
         <v>218</v>
@@ -10873,7 +10877,7 @@
         <v>603</v>
       </c>
       <c r="B92" s="20" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C92" s="20" t="s">
         <v>262</v>
@@ -10903,7 +10907,7 @@
         <v>603</v>
       </c>
       <c r="B93" s="20" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C93" s="20" t="s">
         <v>262</v>
@@ -10933,7 +10937,7 @@
         <v>603</v>
       </c>
       <c r="B94" s="20" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="C94" s="20" t="s">
         <v>262</v>
@@ -10963,10 +10967,10 @@
         <v>604</v>
       </c>
       <c r="B95" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C95" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C95" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D95" s="20" t="s">
         <v>269</v>
@@ -10993,10 +10997,10 @@
         <v>604</v>
       </c>
       <c r="B96" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C96" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C96" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D96" s="20" t="s">
         <v>271</v>
@@ -11023,10 +11027,10 @@
         <v>604</v>
       </c>
       <c r="B97" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C97" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C97" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D97" s="20" t="s">
         <v>272</v>
@@ -11053,10 +11057,10 @@
         <v>604</v>
       </c>
       <c r="B98" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C98" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C98" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D98" s="20" t="s">
         <v>273</v>
@@ -11083,10 +11087,10 @@
         <v>604</v>
       </c>
       <c r="B99" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C99" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C99" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D99" s="20" t="s">
         <v>275</v>
@@ -11113,10 +11117,10 @@
         <v>604</v>
       </c>
       <c r="B100" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C100" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C100" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D100" s="20" t="s">
         <v>276</v>
@@ -11143,10 +11147,10 @@
         <v>604</v>
       </c>
       <c r="B101" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C101" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C101" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D101" s="20" t="s">
         <v>278</v>
@@ -11173,10 +11177,10 @@
         <v>604</v>
       </c>
       <c r="B102" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C102" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C102" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D102" s="20" t="s">
         <v>279</v>
@@ -11203,10 +11207,10 @@
         <v>604</v>
       </c>
       <c r="B103" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C103" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C103" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D103" s="20" t="s">
         <v>281</v>
@@ -11233,10 +11237,10 @@
         <v>604</v>
       </c>
       <c r="B104" s="20" t="s">
+        <v>910</v>
+      </c>
+      <c r="C104" s="20" t="s">
         <v>911</v>
-      </c>
-      <c r="C104" s="20" t="s">
-        <v>912</v>
       </c>
       <c r="D104" s="20" t="s">
         <v>283</v>
@@ -11263,7 +11267,7 @@
         <v>605</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C105" s="20" t="s">
         <v>285</v>
@@ -11293,7 +11297,7 @@
         <v>605</v>
       </c>
       <c r="B106" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C106" s="20" t="s">
         <v>285</v>
@@ -11323,7 +11327,7 @@
         <v>605</v>
       </c>
       <c r="B107" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C107" s="20" t="s">
         <v>285</v>
@@ -11353,7 +11357,7 @@
         <v>605</v>
       </c>
       <c r="B108" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C108" s="20" t="s">
         <v>285</v>
@@ -11383,7 +11387,7 @@
         <v>605</v>
       </c>
       <c r="B109" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C109" s="20" t="s">
         <v>285</v>
@@ -11413,7 +11417,7 @@
         <v>605</v>
       </c>
       <c r="B110" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C110" s="20" t="s">
         <v>285</v>
@@ -11443,7 +11447,7 @@
         <v>605</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C111" s="20" t="s">
         <v>285</v>
@@ -11473,7 +11477,7 @@
         <v>605</v>
       </c>
       <c r="B112" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C112" s="20" t="s">
         <v>285</v>
@@ -11503,7 +11507,7 @@
         <v>605</v>
       </c>
       <c r="B113" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C113" s="20" t="s">
         <v>285</v>
@@ -11533,7 +11537,7 @@
         <v>605</v>
       </c>
       <c r="B114" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C114" s="20" t="s">
         <v>285</v>
@@ -11563,7 +11567,7 @@
         <v>605</v>
       </c>
       <c r="B115" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C115" s="20" t="s">
         <v>285</v>
@@ -11593,7 +11597,7 @@
         <v>605</v>
       </c>
       <c r="B116" s="20" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="C116" s="20" t="s">
         <v>285</v>
@@ -11623,10 +11627,10 @@
         <v>606</v>
       </c>
       <c r="B117" s="20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C117" s="20" t="s">
         <v>914</v>
-      </c>
-      <c r="C117" s="20" t="s">
-        <v>915</v>
       </c>
       <c r="D117" s="20" t="s">
         <v>302</v>
@@ -11653,10 +11657,10 @@
         <v>606</v>
       </c>
       <c r="B118" s="20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C118" s="20" t="s">
         <v>914</v>
-      </c>
-      <c r="C118" s="20" t="s">
-        <v>915</v>
       </c>
       <c r="D118" s="20" t="s">
         <v>303</v>
@@ -11683,10 +11687,10 @@
         <v>606</v>
       </c>
       <c r="B119" s="20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C119" s="20" t="s">
         <v>914</v>
-      </c>
-      <c r="C119" s="20" t="s">
-        <v>915</v>
       </c>
       <c r="D119" s="20" t="s">
         <v>304</v>
@@ -11713,10 +11717,10 @@
         <v>606</v>
       </c>
       <c r="B120" s="20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C120" s="20" t="s">
         <v>914</v>
-      </c>
-      <c r="C120" s="20" t="s">
-        <v>915</v>
       </c>
       <c r="D120" s="20" t="s">
         <v>306</v>
@@ -11743,10 +11747,10 @@
         <v>606</v>
       </c>
       <c r="B121" s="20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C121" s="20" t="s">
         <v>914</v>
-      </c>
-      <c r="C121" s="20" t="s">
-        <v>915</v>
       </c>
       <c r="D121" s="20" t="s">
         <v>308</v>
@@ -11773,10 +11777,10 @@
         <v>606</v>
       </c>
       <c r="B122" s="20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C122" s="20" t="s">
         <v>914</v>
-      </c>
-      <c r="C122" s="20" t="s">
-        <v>915</v>
       </c>
       <c r="D122" s="20" t="s">
         <v>310</v>
@@ -11803,10 +11807,10 @@
         <v>606</v>
       </c>
       <c r="B123" s="20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C123" s="20" t="s">
         <v>914</v>
-      </c>
-      <c r="C123" s="20" t="s">
-        <v>915</v>
       </c>
       <c r="D123" s="20" t="s">
         <v>311</v>
@@ -11833,10 +11837,10 @@
         <v>606</v>
       </c>
       <c r="B124" s="20" t="s">
+        <v>913</v>
+      </c>
+      <c r="C124" s="20" t="s">
         <v>914</v>
-      </c>
-      <c r="C124" s="20" t="s">
-        <v>915</v>
       </c>
       <c r="D124" s="20" t="s">
         <v>312</v>
@@ -11863,10 +11867,10 @@
         <v>607</v>
       </c>
       <c r="B125" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C125" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C125" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D125" s="20" t="s">
         <v>313</v>
@@ -11893,10 +11897,10 @@
         <v>607</v>
       </c>
       <c r="B126" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C126" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C126" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D126" s="20" t="s">
         <v>315</v>
@@ -11923,10 +11927,10 @@
         <v>607</v>
       </c>
       <c r="B127" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C127" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C127" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D127" s="20" t="s">
         <v>317</v>
@@ -11953,10 +11957,10 @@
         <v>607</v>
       </c>
       <c r="B128" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C128" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C128" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D128" s="20" t="s">
         <v>319</v>
@@ -11983,10 +11987,10 @@
         <v>607</v>
       </c>
       <c r="B129" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C129" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C129" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D129" s="20" t="s">
         <v>321</v>
@@ -12013,10 +12017,10 @@
         <v>607</v>
       </c>
       <c r="B130" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C130" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C130" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D130" s="20" t="s">
         <v>323</v>
@@ -12043,10 +12047,10 @@
         <v>607</v>
       </c>
       <c r="B131" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C131" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C131" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D131" s="20" t="s">
         <v>325</v>
@@ -12073,10 +12077,10 @@
         <v>607</v>
       </c>
       <c r="B132" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C132" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C132" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D132" s="20" t="s">
         <v>327</v>
@@ -12103,10 +12107,10 @@
         <v>607</v>
       </c>
       <c r="B133" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C133" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C133" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D133" s="20" t="s">
         <v>329</v>
@@ -12133,10 +12137,10 @@
         <v>607</v>
       </c>
       <c r="B134" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C134" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C134" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D134" s="20" t="s">
         <v>331</v>
@@ -12163,10 +12167,10 @@
         <v>607</v>
       </c>
       <c r="B135" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C135" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C135" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D135" s="20" t="s">
         <v>333</v>
@@ -12193,10 +12197,10 @@
         <v>607</v>
       </c>
       <c r="B136" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C136" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C136" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D136" s="20" t="s">
         <v>334</v>
@@ -12223,10 +12227,10 @@
         <v>607</v>
       </c>
       <c r="B137" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C137" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C137" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D137" s="20" t="s">
         <v>336</v>
@@ -12253,10 +12257,10 @@
         <v>607</v>
       </c>
       <c r="B138" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C138" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C138" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D138" s="20" t="s">
         <v>338</v>
@@ -12283,10 +12287,10 @@
         <v>607</v>
       </c>
       <c r="B139" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C139" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C139" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D139" s="20" t="s">
         <v>339</v>
@@ -12313,10 +12317,10 @@
         <v>607</v>
       </c>
       <c r="B140" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C140" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C140" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D140" s="20" t="s">
         <v>341</v>
@@ -12343,10 +12347,10 @@
         <v>607</v>
       </c>
       <c r="B141" s="20" t="s">
+        <v>915</v>
+      </c>
+      <c r="C141" s="20" t="s">
         <v>916</v>
-      </c>
-      <c r="C141" s="20" t="s">
-        <v>917</v>
       </c>
       <c r="D141" s="20" t="s">
         <v>342</v>
@@ -12373,10 +12377,10 @@
         <v>608</v>
       </c>
       <c r="B142" s="20" t="s">
+        <v>917</v>
+      </c>
+      <c r="C142" s="20" t="s">
         <v>918</v>
-      </c>
-      <c r="C142" s="20" t="s">
-        <v>919</v>
       </c>
       <c r="D142" s="20" t="s">
         <v>344</v>
@@ -12403,10 +12407,10 @@
         <v>608</v>
       </c>
       <c r="B143" s="20" t="s">
+        <v>917</v>
+      </c>
+      <c r="C143" s="20" t="s">
         <v>918</v>
-      </c>
-      <c r="C143" s="20" t="s">
-        <v>919</v>
       </c>
       <c r="D143" s="20" t="s">
         <v>346</v>
@@ -12433,10 +12437,10 @@
         <v>608</v>
       </c>
       <c r="B144" s="20" t="s">
+        <v>917</v>
+      </c>
+      <c r="C144" s="20" t="s">
         <v>918</v>
-      </c>
-      <c r="C144" s="20" t="s">
-        <v>919</v>
       </c>
       <c r="D144" s="20" t="s">
         <v>347</v>
@@ -12463,10 +12467,10 @@
         <v>608</v>
       </c>
       <c r="B145" s="20" t="s">
+        <v>917</v>
+      </c>
+      <c r="C145" s="20" t="s">
         <v>918</v>
-      </c>
-      <c r="C145" s="20" t="s">
-        <v>919</v>
       </c>
       <c r="D145" s="20" t="s">
         <v>348</v>
@@ -12493,10 +12497,10 @@
         <v>608</v>
       </c>
       <c r="B146" s="20" t="s">
+        <v>917</v>
+      </c>
+      <c r="C146" s="20" t="s">
         <v>918</v>
-      </c>
-      <c r="C146" s="20" t="s">
-        <v>919</v>
       </c>
       <c r="D146" s="20" t="s">
         <v>349</v>
@@ -12523,10 +12527,10 @@
         <v>608</v>
       </c>
       <c r="B147" s="20" t="s">
+        <v>917</v>
+      </c>
+      <c r="C147" s="20" t="s">
         <v>918</v>
-      </c>
-      <c r="C147" s="20" t="s">
-        <v>919</v>
       </c>
       <c r="D147" s="20" t="s">
         <v>350</v>
@@ -12556,7 +12560,7 @@
         <v>351</v>
       </c>
       <c r="C148" s="20" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D148" s="20" t="s">
         <v>352</v>
@@ -12586,7 +12590,7 @@
         <v>351</v>
       </c>
       <c r="C149" s="20" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D149" s="20" t="s">
         <v>353</v>
@@ -12613,7 +12617,7 @@
         <v>610</v>
       </c>
       <c r="B150" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C150" s="20" t="s">
         <v>354</v>
@@ -12643,7 +12647,7 @@
         <v>610</v>
       </c>
       <c r="B151" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C151" s="20" t="s">
         <v>354</v>
@@ -12673,7 +12677,7 @@
         <v>610</v>
       </c>
       <c r="B152" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C152" s="20" t="s">
         <v>354</v>
@@ -12703,7 +12707,7 @@
         <v>610</v>
       </c>
       <c r="B153" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C153" s="20" t="s">
         <v>354</v>
@@ -12733,7 +12737,7 @@
         <v>610</v>
       </c>
       <c r="B154" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C154" s="20" t="s">
         <v>354</v>
@@ -12763,7 +12767,7 @@
         <v>610</v>
       </c>
       <c r="B155" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C155" s="20" t="s">
         <v>354</v>
@@ -12793,7 +12797,7 @@
         <v>610</v>
       </c>
       <c r="B156" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C156" s="20" t="s">
         <v>354</v>
@@ -12823,7 +12827,7 @@
         <v>610</v>
       </c>
       <c r="B157" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C157" s="20" t="s">
         <v>354</v>
@@ -12853,7 +12857,7 @@
         <v>610</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C158" s="20" t="s">
         <v>354</v>
@@ -12883,7 +12887,7 @@
         <v>610</v>
       </c>
       <c r="B159" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C159" s="20" t="s">
         <v>354</v>
@@ -12913,7 +12917,7 @@
         <v>610</v>
       </c>
       <c r="B160" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C160" s="20" t="s">
         <v>354</v>
@@ -12943,7 +12947,7 @@
         <v>610</v>
       </c>
       <c r="B161" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C161" s="20" t="s">
         <v>375</v>
@@ -12973,7 +12977,7 @@
         <v>610</v>
       </c>
       <c r="B162" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C162" s="20" t="s">
         <v>375</v>
@@ -12997,7 +13001,7 @@
         <v>610</v>
       </c>
       <c r="B163" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C163" s="20" t="s">
         <v>375</v>
@@ -13021,7 +13025,7 @@
         <v>610</v>
       </c>
       <c r="B164" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C164" s="20" t="s">
         <v>375</v>
@@ -13045,7 +13049,7 @@
         <v>610</v>
       </c>
       <c r="B165" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C165" s="20" t="s">
         <v>375</v>
@@ -13069,7 +13073,7 @@
         <v>610</v>
       </c>
       <c r="B166" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C166" s="20" t="s">
         <v>375</v>
@@ -13093,7 +13097,7 @@
         <v>610</v>
       </c>
       <c r="B167" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C167" s="20" t="s">
         <v>375</v>
@@ -13117,7 +13121,7 @@
         <v>610</v>
       </c>
       <c r="B168" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C168" s="20" t="s">
         <v>375</v>
@@ -13141,7 +13145,7 @@
         <v>610</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C169" s="20" t="s">
         <v>375</v>
@@ -13165,7 +13169,7 @@
         <v>610</v>
       </c>
       <c r="B170" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C170" s="20" t="s">
         <v>375</v>
@@ -13189,7 +13193,7 @@
         <v>610</v>
       </c>
       <c r="B171" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C171" s="20" t="s">
         <v>375</v>
@@ -13213,7 +13217,7 @@
         <v>610</v>
       </c>
       <c r="B172" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C172" s="20" t="s">
         <v>375</v>
@@ -13237,7 +13241,7 @@
         <v>610</v>
       </c>
       <c r="B173" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C173" s="20" t="s">
         <v>375</v>
@@ -13261,7 +13265,7 @@
         <v>610</v>
       </c>
       <c r="B174" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C174" s="20" t="s">
         <v>375</v>
@@ -13285,7 +13289,7 @@
         <v>610</v>
       </c>
       <c r="B175" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C175" s="20" t="s">
         <v>111</v>
@@ -13315,7 +13319,7 @@
         <v>610</v>
       </c>
       <c r="B176" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C176" s="20" t="s">
         <v>111</v>
@@ -13339,7 +13343,7 @@
         <v>610</v>
       </c>
       <c r="B177" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C177" s="20" t="s">
         <v>111</v>
@@ -13363,7 +13367,7 @@
         <v>610</v>
       </c>
       <c r="B178" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C178" s="20" t="s">
         <v>111</v>
@@ -13387,7 +13391,7 @@
         <v>610</v>
       </c>
       <c r="B179" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C179" s="20" t="s">
         <v>111</v>
@@ -13411,7 +13415,7 @@
         <v>610</v>
       </c>
       <c r="B180" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C180" s="20" t="s">
         <v>111</v>
@@ -13435,7 +13439,7 @@
         <v>610</v>
       </c>
       <c r="B181" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C181" s="20" t="s">
         <v>111</v>
@@ -13459,7 +13463,7 @@
         <v>610</v>
       </c>
       <c r="B182" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C182" s="20" t="s">
         <v>111</v>
@@ -13483,7 +13487,7 @@
         <v>610</v>
       </c>
       <c r="B183" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C183" s="20" t="s">
         <v>111</v>
@@ -13507,7 +13511,7 @@
         <v>610</v>
       </c>
       <c r="B184" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C184" s="20" t="s">
         <v>112</v>
@@ -13537,7 +13541,7 @@
         <v>610</v>
       </c>
       <c r="B185" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C185" s="20" t="s">
         <v>112</v>
@@ -13561,7 +13565,7 @@
         <v>610</v>
       </c>
       <c r="B186" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C186" s="20" t="s">
         <v>112</v>
@@ -13585,7 +13589,7 @@
         <v>610</v>
       </c>
       <c r="B187" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C187" s="20" t="s">
         <v>112</v>
@@ -13609,7 +13613,7 @@
         <v>610</v>
       </c>
       <c r="B188" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C188" s="20" t="s">
         <v>112</v>
@@ -13633,7 +13637,7 @@
         <v>610</v>
       </c>
       <c r="B189" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C189" s="20" t="s">
         <v>112</v>
@@ -13657,7 +13661,7 @@
         <v>610</v>
       </c>
       <c r="B190" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C190" s="20" t="s">
         <v>112</v>
@@ -13681,7 +13685,7 @@
         <v>610</v>
       </c>
       <c r="B191" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C191" s="20" t="s">
         <v>112</v>
@@ -13705,7 +13709,7 @@
         <v>610</v>
       </c>
       <c r="B192" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C192" s="20" t="s">
         <v>112</v>
@@ -13729,7 +13733,7 @@
         <v>610</v>
       </c>
       <c r="B193" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C193" s="20" t="s">
         <v>112</v>
@@ -13753,7 +13757,7 @@
         <v>610</v>
       </c>
       <c r="B194" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C194" s="20" t="s">
         <v>112</v>
@@ -13777,7 +13781,7 @@
         <v>610</v>
       </c>
       <c r="B195" s="20" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C195" s="20" t="s">
         <v>112</v>
@@ -13804,7 +13808,7 @@
         <v>113</v>
       </c>
       <c r="C196" s="20" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="D196" s="20" t="s">
         <v>431</v>
@@ -13960,7 +13964,7 @@
         <v>113</v>
       </c>
       <c r="C202" s="20" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D202" s="20" t="s">
         <v>442</v>
@@ -14080,16 +14084,16 @@
   <sheetData>
     <row r="1" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>899</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>895</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>900</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>896</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>901</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -14097,7 +14101,7 @@
         <v>444</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20">
@@ -14288,142 +14292,142 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B1" s="19" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1" s="19" t="s">
         <v>973</v>
       </c>
-      <c r="C1" s="19" t="s">
-        <v>974</v>
-      </c>
       <c r="D1" s="19" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="56" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2" s="56" t="s">
         <v>924</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="C2" s="56" t="s">
+        <v>991</v>
+      </c>
+      <c r="D2" s="56" t="s">
         <v>925</v>
-      </c>
-      <c r="C2" s="56" t="s">
-        <v>992</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="56" t="s">
+        <v>926</v>
+      </c>
+      <c r="B3" s="56" t="s">
         <v>927</v>
       </c>
-      <c r="B3" s="56" t="s">
-        <v>928</v>
-      </c>
       <c r="C3" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="56" t="s">
+        <v>928</v>
+      </c>
+      <c r="B4" s="56" t="s">
         <v>929</v>
       </c>
-      <c r="B4" s="56" t="s">
-        <v>930</v>
-      </c>
       <c r="C4" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="56" t="s">
+        <v>930</v>
+      </c>
+      <c r="B5" s="56" t="s">
         <v>931</v>
       </c>
-      <c r="B5" s="56" t="s">
-        <v>932</v>
-      </c>
       <c r="C5" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="56" t="s">
+        <v>932</v>
+      </c>
+      <c r="B6" s="56" t="s">
         <v>933</v>
       </c>
-      <c r="B6" s="56" t="s">
-        <v>934</v>
-      </c>
       <c r="C6" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="56" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C7" s="56" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="56" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B8" s="56" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C8" s="56" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="56" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B9" s="56" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C9" s="56" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="56" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B10" s="56" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C10" s="56" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -14431,27 +14435,27 @@
         <v>46</v>
       </c>
       <c r="B11" s="56" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="56" t="s">
+        <v>939</v>
+      </c>
+      <c r="B12" s="56" t="s">
         <v>940</v>
       </c>
-      <c r="B12" s="56" t="s">
-        <v>941</v>
-      </c>
       <c r="C12" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -14459,52 +14463,52 @@
         <v>8</v>
       </c>
       <c r="B13" s="56" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C13" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="56" t="s">
+        <v>942</v>
+      </c>
+      <c r="B14" s="56" t="s">
         <v>943</v>
       </c>
-      <c r="B14" s="56" t="s">
-        <v>944</v>
-      </c>
       <c r="C14" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="56" t="s">
+        <v>944</v>
+      </c>
+      <c r="B15" s="56" t="s">
         <v>945</v>
       </c>
-      <c r="B15" s="56" t="s">
-        <v>946</v>
-      </c>
       <c r="C15" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D15" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="56" t="s">
+        <v>946</v>
+      </c>
+      <c r="B16" s="56" t="s">
         <v>947</v>
       </c>
-      <c r="B16" s="56" t="s">
-        <v>948</v>
-      </c>
       <c r="C16" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D16" s="56"/>
     </row>
@@ -14513,55 +14517,55 @@
         <v>9</v>
       </c>
       <c r="B17" s="56" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C17" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="56" t="s">
+        <v>949</v>
+      </c>
+      <c r="B18" s="56" t="s">
         <v>950</v>
       </c>
-      <c r="B18" s="56" t="s">
-        <v>951</v>
-      </c>
       <c r="C18" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="56" t="s">
+        <v>951</v>
+      </c>
+      <c r="B19" s="56" t="s">
         <v>952</v>
       </c>
-      <c r="B19" s="56" t="s">
-        <v>953</v>
-      </c>
       <c r="C19" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="56" t="s">
+        <v>953</v>
+      </c>
+      <c r="B20" s="56" t="s">
         <v>954</v>
       </c>
-      <c r="B20" s="56" t="s">
-        <v>955</v>
-      </c>
       <c r="C20" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="27" x14ac:dyDescent="0.3">
@@ -14569,10 +14573,10 @@
         <v>671</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C21" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D21" s="56"/>
     </row>
@@ -14581,39 +14585,39 @@
         <v>672</v>
       </c>
       <c r="B22" s="56" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C22" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D22" s="56"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="56" t="s">
+        <v>955</v>
+      </c>
+      <c r="B23" s="56" t="s">
         <v>956</v>
       </c>
-      <c r="B23" s="56" t="s">
-        <v>957</v>
-      </c>
       <c r="C23" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="56" t="s">
+        <v>957</v>
+      </c>
+      <c r="B24" s="56" t="s">
         <v>958</v>
       </c>
-      <c r="B24" s="56" t="s">
-        <v>959</v>
-      </c>
       <c r="C24" s="56" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -14621,41 +14625,41 @@
         <v>15</v>
       </c>
       <c r="B25" s="56" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="C25" s="56" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="56" t="s">
+        <v>960</v>
+      </c>
+      <c r="B26" s="56" t="s">
         <v>961</v>
       </c>
-      <c r="B26" s="56" t="s">
-        <v>962</v>
-      </c>
       <c r="C26" s="56" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="56" t="s">
+        <v>962</v>
+      </c>
+      <c r="B27" s="56" t="s">
         <v>963</v>
       </c>
-      <c r="B27" s="56" t="s">
-        <v>964</v>
-      </c>
       <c r="C27" s="56" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -14663,41 +14667,41 @@
         <v>16</v>
       </c>
       <c r="B28" s="56" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="C28" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="56" t="s">
+        <v>965</v>
+      </c>
+      <c r="B29" s="56" t="s">
         <v>966</v>
       </c>
-      <c r="B29" s="56" t="s">
-        <v>967</v>
-      </c>
       <c r="C29" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="56" t="s">
+        <v>967</v>
+      </c>
+      <c r="B30" s="56" t="s">
         <v>968</v>
       </c>
-      <c r="B30" s="56" t="s">
-        <v>969</v>
-      </c>
       <c r="C30" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -14705,38 +14709,38 @@
         <v>26</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="C31" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="56" t="s">
+        <v>970</v>
+      </c>
+      <c r="B32" s="56" t="s">
         <v>971</v>
       </c>
-      <c r="B32" s="56" t="s">
-        <v>972</v>
-      </c>
       <c r="C32" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="56" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B33" s="56" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="C33" s="56" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="D33" s="56"/>
     </row>
@@ -14755,7 +14759,7 @@
         <v>685</v>
       </c>
       <c r="B35" s="56" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C35" s="56"/>
       <c r="D35" s="56"/>
@@ -14765,7 +14769,7 @@
         <v>687</v>
       </c>
       <c r="B36" s="56" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="C36" s="56"/>
       <c r="D36" s="56"/>
@@ -14775,7 +14779,7 @@
         <v>689</v>
       </c>
       <c r="B37" s="56" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="C37" s="56"/>
       <c r="D37" s="56"/>
@@ -14785,7 +14789,7 @@
         <v>691</v>
       </c>
       <c r="B38" s="58" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C38" s="56"/>
       <c r="D38" s="56"/>
@@ -14795,7 +14799,7 @@
         <v>693</v>
       </c>
       <c r="B39" s="58" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C39" s="56"/>
       <c r="D39" s="56"/>
@@ -14805,7 +14809,7 @@
         <v>694</v>
       </c>
       <c r="B40" s="58" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C40" s="56"/>
       <c r="D40" s="56"/>
@@ -14815,7 +14819,7 @@
         <v>695</v>
       </c>
       <c r="B41" s="58" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C41" s="56"/>
       <c r="D41" s="56"/>
@@ -14825,7 +14829,7 @@
         <v>697</v>
       </c>
       <c r="B42" s="58" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C42" s="56"/>
       <c r="D42" s="56"/>
@@ -14855,10 +14859,10 @@
         <v>40</v>
       </c>
       <c r="B45" s="56" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="C45" s="56" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="D45" s="56"/>
     </row>
